--- a/server/templates/wage-bill-template.xlsx
+++ b/server/templates/wage-bill-template.xlsx
@@ -372,7 +372,7 @@
     </r>
   </si>
   <si>
-    <t>BILL FOR THE MONTH OF {{MONTH_LABEL}}</t>
+    <t>FOR THE MONTH OF {{MONTH_LABEL}}</t>
   </si>
   <si>
     <r>
